--- a/hrcheck/examples/本月花名册_修复建议.xlsx
+++ b/hrcheck/examples/本月花名册_修复建议.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N29"/>
+  <dimension ref="A1:Q29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -455,14 +455,14 @@
       </c>
       <c r="H1" t="inlineStr">
         <is>
+          <t>修复方式</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
           <t>建议修复值</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>修复方式</t>
-        </is>
-      </c>
       <c r="J1" t="inlineStr">
         <is>
           <t>置信度</t>
@@ -475,17 +475,32 @@
       </c>
       <c r="L1" t="inlineStr">
         <is>
+          <t>可删除此行</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
           <t>详细说明</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>是否采纳</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>是否删除此行</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
         <is>
           <t>人工修正值</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>备注</t>
         </is>
       </c>
     </row>
@@ -521,29 +536,40 @@
           <t>工号 [E00001] 重复出现 2 次</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr"/>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>保留原工号</t>
+        </is>
+      </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>delete_duplicate</t>
+          <t>E00001</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>中</t>
+          <t>高</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>工号 E00001 重复，请确认删除重复记录或更正工号</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr"/>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>工号 E00001 重复，建议保留此行（请确认其他重复行是否删除）</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -577,12 +603,12 @@
           <t>工号 [E00001] 重复出现 2 次</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>delete_duplicate</t>
-        </is>
-      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>删除重复行</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
           <t>中</t>
@@ -595,11 +621,18 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>工号 E00001 重复，请确认删除重复记录或更正工号</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr"/>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>工号 E00001 重复，建议删除此行（或填写'人工修正值'改为新工号）</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -633,12 +666,12 @@
           <t>字段 [姓名] 为空</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>fill_empty</t>
-        </is>
-      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>补空字段</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
           <t>低</t>
@@ -651,11 +684,18 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>字段 姓名 需要补充信息</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr"/>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>请人工补充员工姓名</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -691,14 +731,14 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
+          <t>补空字段</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
           <t>E00047</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>fill_empty</t>
-        </is>
-      </c>
       <c r="J5" t="inlineStr">
         <is>
           <t>中</t>
@@ -711,11 +751,18 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>建议补充上级为同部门经理: 赵艳</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr"/>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>建议补充上级为同部门经理: 赵艳(E00047)</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -751,14 +798,14 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
+          <t>补空字段</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
           <t>行政部</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>fill_empty</t>
-        </is>
-      </c>
       <c r="J6" t="inlineStr">
         <is>
           <t>中</t>
@@ -771,11 +818,18 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>字段 部门 需要补充信息</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr"/>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>根据岗位'行政专员'建议部门: 行政部</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -811,14 +865,14 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
+          <t>补空字段</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
           <t>E00047</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>fill_empty</t>
-        </is>
-      </c>
       <c r="J7" t="inlineStr">
         <is>
           <t>中</t>
@@ -831,11 +885,18 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>建议补充上级为同部门经理: 赵艳</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr"/>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>建议补充上级为同部门经理: 赵艳(E00047)</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -871,17 +932,13 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>E00012</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>fill_empty</t>
-        </is>
-      </c>
+          <t>补空字段</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
-          <t>中</t>
+          <t>低</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -891,11 +948,18 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>建议补充上级为同部门主管: 罗静</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr"/>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>字段 直属上级工号 需要补充信息</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -931,17 +995,13 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>E00016</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>fill_empty</t>
-        </is>
-      </c>
+          <t>补空字段</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
         <is>
-          <t>中</t>
+          <t>低</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -951,11 +1011,18 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>建议补充上级为同部门总监: 王静</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr"/>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>字段 直属上级工号 需要补充信息</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -991,14 +1058,14 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
+          <t>补空字段</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
           <t>E00022</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>fill_empty</t>
-        </is>
-      </c>
       <c r="J10" t="inlineStr">
         <is>
           <t>中</t>
@@ -1011,11 +1078,18 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>建议补充上级为同部门经理: 黄磊</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr"/>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>建议补充上级为同部门经理: 黄磊(E00022)</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1051,14 +1125,14 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
+          <t>补空字段</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
           <t>E00019</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>fill_empty</t>
-        </is>
-      </c>
       <c r="J11" t="inlineStr">
         <is>
           <t>中</t>
@@ -1071,11 +1145,18 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>建议补充上级为同部门经理: 黄桂英</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr"/>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>建议补充上级为同部门经理: 黄桂英(E00019)</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1111,17 +1192,13 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>E00030</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>fill_empty</t>
-        </is>
-      </c>
+          <t>补空字段</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
-          <t>中</t>
+          <t>低</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1131,11 +1208,18 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>建议补充上级为同部门经理: 马敏</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr"/>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>字段 直属上级工号 需要补充信息</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1171,14 +1255,14 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
+          <t>补空字段</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
           <t>E00005</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>fill_empty</t>
-        </is>
-      </c>
       <c r="J13" t="inlineStr">
         <is>
           <t>中</t>
@@ -1191,11 +1275,18 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>建议补充上级为同部门经理: 周博</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr"/>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>建议补充上级为同部门经理: 周博(E00005)</t>
+        </is>
+      </c>
       <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="inlineStr"/>
+      <c r="Q13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1231,14 +1322,14 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
+          <t>补空字段</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
           <t>E00030</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>fill_empty</t>
-        </is>
-      </c>
       <c r="J14" t="inlineStr">
         <is>
           <t>中</t>
@@ -1251,11 +1342,18 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>建议补充上级为同部门经理: 马敏</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr"/>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>建议补充上级为同部门经理: 马敏(E00030)</t>
+        </is>
+      </c>
       <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -1291,14 +1389,14 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
+          <t>补空字段</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
           <t>E00010</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>fill_empty</t>
-        </is>
-      </c>
       <c r="J15" t="inlineStr">
         <is>
           <t>中</t>
@@ -1311,11 +1409,18 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>建议补充上级为同部门经理: 刘佳</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr"/>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>建议补充上级为同部门经理: 刘佳(E00010)</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" t="inlineStr"/>
+      <c r="Q15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -1351,14 +1456,14 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
+          <t>补空字段</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
           <t>E00010</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>fill_empty</t>
-        </is>
-      </c>
       <c r="J16" t="inlineStr">
         <is>
           <t>中</t>
@@ -1371,11 +1476,18 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>建议补充上级为同部门经理: 刘佳</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr"/>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>建议补充上级为同部门经理: 刘佳(E00010)</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr"/>
+      <c r="P16" t="inlineStr"/>
+      <c r="Q16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -1409,12 +1521,12 @@
           <t>字段 [岗位] 为空</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>fill_empty</t>
-        </is>
-      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>补空字段</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr">
         <is>
           <t>低</t>
@@ -1427,11 +1539,18 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>字段 岗位 需要补充信息</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr"/>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>请人工补充岗位信息</t>
+        </is>
+      </c>
       <c r="N17" t="inlineStr"/>
+      <c r="O17" t="inlineStr"/>
+      <c r="P17" t="inlineStr"/>
+      <c r="Q17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -1465,12 +1584,12 @@
           <t>字段 [直属上级工号] 为空</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>fill_empty</t>
-        </is>
-      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>补空字段</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr">
         <is>
           <t>低</t>
@@ -1483,11 +1602,18 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
           <t>字段 直属上级工号 需要补充信息</t>
         </is>
       </c>
-      <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
+      <c r="O18" t="inlineStr"/>
+      <c r="P18" t="inlineStr"/>
+      <c r="Q18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -1523,14 +1649,14 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
+          <t>补空字段</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
           <t>E00010</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>fill_empty</t>
-        </is>
-      </c>
       <c r="J19" t="inlineStr">
         <is>
           <t>中</t>
@@ -1543,11 +1669,18 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>建议补充上级为同部门经理: 刘佳</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr"/>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>建议补充上级为同部门经理: 刘佳(E00010)</t>
+        </is>
+      </c>
       <c r="N19" t="inlineStr"/>
+      <c r="O19" t="inlineStr"/>
+      <c r="P19" t="inlineStr"/>
+      <c r="Q19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -1583,14 +1716,14 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
+          <t>补空字段</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
           <t>E00030</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>fill_empty</t>
-        </is>
-      </c>
       <c r="J20" t="inlineStr">
         <is>
           <t>中</t>
@@ -1603,11 +1736,18 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>建议补充上级为同部门经理: 马敏</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr"/>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>建议补充上级为同部门经理: 马敏(E00030)</t>
+        </is>
+      </c>
       <c r="N20" t="inlineStr"/>
+      <c r="O20" t="inlineStr"/>
+      <c r="P20" t="inlineStr"/>
+      <c r="Q20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -1643,14 +1783,14 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
+          <t>修正日期格式</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
           <t>2025-13-45</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>fix_date_format</t>
-        </is>
-      </c>
       <c r="J21" t="inlineStr">
         <is>
           <t>高</t>
@@ -1663,11 +1803,18 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
           <t>建议将日期格式化为 YYYY-MM-DD: 2025-13-45</t>
         </is>
       </c>
-      <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
+      <c r="O21" t="inlineStr"/>
+      <c r="P21" t="inlineStr"/>
+      <c r="Q21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -1701,12 +1848,12 @@
           <t>字段 [入职日期] 日期在未来: 2030-01-01</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr"/>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>verify_future_date</t>
-        </is>
-      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>确认未来日期</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr">
         <is>
           <t>中</t>
@@ -1719,11 +1866,18 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>日期 2030-01-01 在未来，请确认是否为预期（如预入职）</t>
-        </is>
-      </c>
-      <c r="M22" t="inlineStr"/>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>日期 2030-01-01 在未来，请确认是否为预入职/预离职（是则人工修正值填'保留'）</t>
+        </is>
+      </c>
       <c r="N22" t="inlineStr"/>
+      <c r="O22" t="inlineStr"/>
+      <c r="P22" t="inlineStr"/>
+      <c r="Q22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -1757,12 +1911,12 @@
           <t>部门 [神秘部门] 不在有效部门列表中</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr"/>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>fix_department</t>
-        </is>
-      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>修正部门</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr">
         <is>
           <t>低</t>
@@ -1775,11 +1929,18 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>有效部门: 总经办, 人力资源部, 财务部, 行政部, 技术部, 产品部, 设计部, 市场部, 销售部, 运营部...</t>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr"/>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>未匹配到有效部门 | 可选: 总经办, 人力资源部, 财务部, 行政部, 技术部, 产品部, 设计部, 市场部, 销售部, 运营部...</t>
+        </is>
+      </c>
       <c r="N23" t="inlineStr"/>
+      <c r="O23" t="inlineStr"/>
+      <c r="P23" t="inlineStr"/>
+      <c r="Q23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -1813,12 +1974,12 @@
           <t>用工类型 [随意类型] 不在有效值列表中</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr"/>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>fix_employment_type</t>
-        </is>
-      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>修正用工类型</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr">
         <is>
           <t>低</t>
@@ -1831,11 +1992,18 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
           <t>有效类型: 正式, 试用期, 实习, 外包, 派遣, 兼职, 劳务</t>
         </is>
       </c>
-      <c r="M24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
+      <c r="O24" t="inlineStr"/>
+      <c r="P24" t="inlineStr"/>
+      <c r="Q24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -1869,12 +2037,12 @@
           <t>上下级关系存在循环引用: E00013 -&gt; E00010 -&gt; E00008 -&gt; E00013</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr"/>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>break_cycle</t>
-        </is>
-      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>打破上级循环</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr">
         <is>
           <t>低</t>
@@ -1887,11 +2055,18 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>存在循环引用: E00013 -&gt; E00010 -&gt; E00008 -&gt; E00013，请调整上级关系</t>
-        </is>
-      </c>
-      <c r="M25" t="inlineStr"/>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>存在循环引用: E00013 -&gt; E00010 -&gt; E00008 -&gt; E00013，请在人工修正值中填写正确的上级工号</t>
+        </is>
+      </c>
       <c r="N25" t="inlineStr"/>
+      <c r="O25" t="inlineStr"/>
+      <c r="P25" t="inlineStr"/>
+      <c r="Q25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -1925,12 +2100,12 @@
           <t>上下级关系存在循环引用: E00013 -&gt; E00010 -&gt; E00008 -&gt; E00013</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr"/>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>break_cycle</t>
-        </is>
-      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>打破上级循环</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr">
         <is>
           <t>低</t>
@@ -1943,11 +2118,18 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>存在循环引用: E00013 -&gt; E00010 -&gt; E00008 -&gt; E00013，请调整上级关系</t>
-        </is>
-      </c>
-      <c r="M26" t="inlineStr"/>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>存在循环引用: E00013 -&gt; E00010 -&gt; E00008 -&gt; E00013，请在人工修正值中填写正确的上级工号</t>
+        </is>
+      </c>
       <c r="N26" t="inlineStr"/>
+      <c r="O26" t="inlineStr"/>
+      <c r="P26" t="inlineStr"/>
+      <c r="Q26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -1981,12 +2163,12 @@
           <t>上下级关系存在循环引用: E00013 -&gt; E00010 -&gt; E00008 -&gt; E00013</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr"/>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>break_cycle</t>
-        </is>
-      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>打破上级循环</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr">
         <is>
           <t>低</t>
@@ -1999,11 +2181,18 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>存在循环引用: E00013 -&gt; E00010 -&gt; E00008 -&gt; E00013，请调整上级关系</t>
-        </is>
-      </c>
-      <c r="M27" t="inlineStr"/>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>存在循环引用: E00013 -&gt; E00010 -&gt; E00008 -&gt; E00013，请在人工修正值中填写正确的上级工号</t>
+        </is>
+      </c>
       <c r="N27" t="inlineStr"/>
+      <c r="O27" t="inlineStr"/>
+      <c r="P27" t="inlineStr"/>
+      <c r="Q27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -2039,14 +2228,14 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
+          <t>补充离职日期</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
           <t>2026-06-11</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>add_resign_date</t>
-        </is>
-      </c>
       <c r="J28" t="inlineStr">
         <is>
           <t>中</t>
@@ -2059,11 +2248,18 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>状态为离职但缺少离职日期，建议补充: 2026-06-11（请确认）</t>
-        </is>
-      </c>
-      <c r="M28" t="inlineStr"/>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>状态为离职但缺少离职日期，建议补充: 2026-06-11（请人工确认）</t>
+        </is>
+      </c>
       <c r="N28" t="inlineStr"/>
+      <c r="O28" t="inlineStr"/>
+      <c r="P28" t="inlineStr"/>
+      <c r="Q28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -2097,12 +2293,12 @@
           <t>在职状态与入职/离职日期冲突: 离职日期 (2018-08-24) 早于入职日期 (2030-01-01)</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr"/>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>fix_status_conflict</t>
-        </is>
-      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>解决状态冲突</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr">
         <is>
           <t>低</t>
@@ -2115,11 +2311,18 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>状态冲突: 在职状态与入职/离职日期冲突: 离职日期 (2018-08-24) 早于入职日期 (2030-01-01)，请人工确认</t>
-        </is>
-      </c>
-      <c r="M29" t="inlineStr"/>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>状态冲突: 在职状态与入职/离职日期冲突: 离职日期 (2018-08-24) 早于入职日期 (2030-01-01)，请人工修正（状态/入职日期/离职日期任选其一修改）</t>
+        </is>
+      </c>
       <c r="N29" t="inlineStr"/>
+      <c r="O29" t="inlineStr"/>
+      <c r="P29" t="inlineStr"/>
+      <c r="Q29" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
